--- a/uGridNet Start Packet/uGrid_Input.xlsx
+++ b/uGridNet Start Packet/uGrid_Input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phy\Documents\OnePower\Python Models Local Copy\uGrid-master-GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mostation/Projects/1PWR/uGrid_uGridNet/uGridNet Start Packet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B03C34-6618-477A-B621-2B6EE2947AA3}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B0ADF-1277-AA4C-8C3E-E046D261414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3108" yWindow="2088" windowWidth="17280" windowHeight="8964" activeTab="4" xr2:uid="{68709F03-E2F0-4CA3-951F-ABB4DD9E87C4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSO" sheetId="1" r:id="rId1"/>
@@ -18,24 +18,35 @@
     <sheet name="Tech" sheetId="3" r:id="rId3"/>
     <sheet name="Solar" sheetId="4" r:id="rId4"/>
     <sheet name="Net" sheetId="5" r:id="rId5"/>
+    <sheet name="NetComponentsCost" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="headers">[1]PARTS!$A$1:$AMJ$1</definedName>
+    <definedName name="parts">[1]PARTS!$A$3:$AMJ$1432</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>maxGen</t>
   </si>
@@ -82,6 +93,9 @@
     <t>output_name</t>
   </si>
   <si>
+    <t>alt_plot_test</t>
+  </si>
+  <si>
     <t>lifetime</t>
   </si>
   <si>
@@ -190,6 +204,18 @@
     <t>Cost_taxes</t>
   </si>
   <si>
+    <t>tariff_hillclimb_multiplier</t>
+  </si>
+  <si>
+    <t>Cost_Trans_wire</t>
+  </si>
+  <si>
+    <t>Cost_Housing_Wiring</t>
+  </si>
+  <si>
+    <t>assuming $0.50/m</t>
+  </si>
+  <si>
     <t>smart</t>
   </si>
   <si>
@@ -199,7 +225,10 @@
     <t>Batt_Charge_Limit</t>
   </si>
   <si>
-    <t>tariff_hillclimb_multiplier</t>
+    <t>trans_losses</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
   <si>
     <t>longitude</t>
@@ -208,9 +237,6 @@
     <t>latitude</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
     <t>timezone</t>
   </si>
   <si>
@@ -235,15 +261,6 @@
     <t>f_inv</t>
   </si>
   <si>
-    <t>trans_losses</t>
-  </si>
-  <si>
-    <t>assuming $0.50/m</t>
-  </si>
-  <si>
-    <t>Cost_Trans_wire</t>
-  </si>
-  <si>
     <t>reformatScaler</t>
   </si>
   <si>
@@ -271,9 +288,6 @@
     <t>Cost_kWh</t>
   </si>
   <si>
-    <t>Cost_Housing_Wiring</t>
-  </si>
-  <si>
     <t>restoration_time_MV</t>
   </si>
   <si>
@@ -286,23 +300,76 @@
     <t>prob_LV</t>
   </si>
   <si>
-    <t>alt_plot_test</t>
-  </si>
-  <si>
     <t>repeats</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>UnitPrice</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - MV – Start</t>
+  </si>
+  <si>
+    <t>Assembly - Step - Down – Transformer</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - MV – Mid</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - MV - Bend &lt;30</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - MV - Bend &gt;30</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - MV – End</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - LV – Mid</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - LV - Bend &lt;60</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - LV - Bend &gt;60</t>
+  </si>
+  <si>
+    <t>Assembly - Pole - LV – End</t>
+  </si>
+  <si>
+    <t>Wire – MV</t>
+  </si>
+  <si>
+    <t>Wire – LV</t>
+  </si>
+  <si>
+    <t>Wire – LineDrop</t>
+  </si>
+  <si>
+    <t>Assembly – Meter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -313,10 +380,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -325,8 +401,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -342,6 +431,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="PARTS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -640,27 +742,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810FAEA2-4EF8-4AD5-9CE0-4B60A3CE1971}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="10" width="3.1640625" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="2.83203125" customWidth="1"/>
+    <col min="13" max="13" width="4" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>50</v>
       </c>
@@ -752,177 +853,178 @@
         <v>0.95</v>
       </c>
       <c r="O2" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5ADBEA2-0E58-4F34-AFD4-59ED09832C5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AM3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" customWidth="1"/>
+    <col min="2" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="4.83203125" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="15.83203125" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="28.6640625" customWidth="1"/>
+    <col min="20" max="20" width="9.1640625" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="17.83203125" customWidth="1"/>
+    <col min="23" max="23" width="22.83203125" customWidth="1"/>
+    <col min="24" max="24" width="19.5" customWidth="1"/>
+    <col min="25" max="25" width="23.1640625" customWidth="1"/>
+    <col min="26" max="26" width="17.6640625" customWidth="1"/>
+    <col min="27" max="27" width="21.1640625" customWidth="1"/>
+    <col min="28" max="28" width="19.83203125" customWidth="1"/>
+    <col min="29" max="29" width="18.83203125" customWidth="1"/>
+    <col min="30" max="30" width="13.33203125" customWidth="1"/>
+    <col min="31" max="31" width="12.5" customWidth="1"/>
+    <col min="32" max="32" width="19.1640625" customWidth="1"/>
+    <col min="33" max="33" width="12.5" customWidth="1"/>
+    <col min="34" max="34" width="19.83203125" customWidth="1"/>
+    <col min="35" max="35" width="17.6640625" customWidth="1"/>
+    <col min="36" max="36" width="10" customWidth="1"/>
+    <col min="37" max="37" width="21.83203125" customWidth="1"/>
+    <col min="38" max="38" width="15.83203125" customWidth="1"/>
+    <col min="39" max="39" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="X1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AB1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AH1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AI1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AJ1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM1" t="s">
         <v>54</v>
       </c>
-      <c r="AL1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>15</v>
       </c>
@@ -1043,45 +1145,46 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="O3" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B00D0BC-366A-4E86-BC5F-EB05356D5715}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1096,51 +1199,52 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26A88A2-799B-4631-B6FE-A8330968DD02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2005</v>
       </c>
@@ -1176,75 +1280,75 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3256D70B-7508-42A8-AA62-A295C44165D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1270,7 +1374,7 @@
         <v>27.590275999999999</v>
       </c>
       <c r="I2">
-        <v>0.34343958370448058</v>
+        <v>0.34343958370448102</v>
       </c>
       <c r="J2">
         <f>7*24</f>
@@ -1287,10 +1391,150 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="4">
+        <v>4843.6050704225399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2052.7914788732401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="4">
+        <v>193.130345070423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="4">
+        <v>305.027464788732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="4">
+        <v>430.23233098591601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="4">
+        <v>193.33028169014099</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="4">
+        <v>52.491533802816903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="4">
+        <v>80.771533802816904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="4">
+        <v>114.961392957746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="5">
+        <v>81.239999999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="5">
+        <v>186.88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/uGridNet Start Packet/uGrid_Input.xlsx
+++ b/uGridNet Start Packet/uGrid_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mostation/Projects/1PWR/uGrid_uGridNet/uGridNet Start Packet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B0ADF-1277-AA4C-8C3E-E046D261414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BF7063-E794-0A49-A26D-04BF1CB781F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,7 +355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -370,6 +370,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFA9B7C6"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -401,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -416,6 +428,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,7 +758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
     <col min="2" max="2" width="7.1640625" customWidth="1"/>
@@ -761,7 +775,7 @@
     <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -808,7 +822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>50</v>
       </c>
@@ -865,7 +879,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AM3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.1640625" customWidth="1"/>
     <col min="2" max="5" width="5" customWidth="1"/>
@@ -905,7 +919,7 @@
     <col min="39" max="39" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -1024,7 +1038,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39">
       <c r="A2">
         <v>15</v>
       </c>
@@ -1145,7 +1159,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39">
       <c r="O3" t="s">
         <v>55</v>
       </c>
@@ -1162,7 +1176,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
@@ -1170,7 +1184,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -1184,7 +1198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1207,9 +1221,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>60</v>
       </c>
@@ -1244,7 +1258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>2005</v>
       </c>
@@ -1287,8 +1301,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -1304,7 +1318,7 @@
     <col min="13" max="13" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>71</v>
       </c>
@@ -1348,7 +1362,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="16">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1367,11 +1381,11 @@
       <c r="F2">
         <v>500</v>
       </c>
-      <c r="G2">
-        <v>-29.178957</v>
-      </c>
-      <c r="H2">
-        <v>27.590275999999999</v>
+      <c r="G2" s="6">
+        <v>-29.873325000000001</v>
+      </c>
+      <c r="H2" s="6">
+        <v>28.61674</v>
       </c>
       <c r="I2">
         <v>0.34343958370448102</v>
@@ -1393,6 +1407,9 @@
       <c r="N2">
         <v>1</v>
       </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="D3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -1403,13 +1420,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>85</v>
       </c>
@@ -1417,7 +1434,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>87</v>
       </c>
@@ -1425,7 +1442,7 @@
         <v>4843.6050704225399</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>88</v>
       </c>
@@ -1433,7 +1450,7 @@
         <v>2052.7914788732401</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>89</v>
       </c>
@@ -1441,7 +1458,7 @@
         <v>193.130345070423</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
@@ -1449,7 +1466,7 @@
         <v>305.027464788732</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
@@ -1457,7 +1474,7 @@
         <v>430.23233098591601</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -1465,7 +1482,7 @@
         <v>193.33028169014099</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
@@ -1473,7 +1490,7 @@
         <v>52.491533802816903</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>94</v>
       </c>
@@ -1481,7 +1498,7 @@
         <v>80.771533802816904</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>95</v>
       </c>
@@ -1489,7 +1506,7 @@
         <v>114.961392957746</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>96</v>
       </c>
@@ -1497,7 +1514,7 @@
         <v>81.239999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>97</v>
       </c>
@@ -1505,7 +1522,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>98</v>
       </c>
@@ -1513,7 +1530,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>99</v>
       </c>
@@ -1521,7 +1538,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>100</v>
       </c>
